--- a/education_forms/040_scholarship_reference_submission--education_forms.xlsx
+++ b/education_forms/040_scholarship_reference_submission--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>submitter</t>
+          <t>is_submitter</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Submitter</t>
+          <t>Is the referee a submitter?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>referee_name</t>
+          <t>submitter_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>referee_name</t>
+          <t>Submitter Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>referee_title</t>
+          <t>referee_name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>referee_title</t>
+          <t>Referee Name</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>referee_institution</t>
+          <t>referee_title</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>referee_institution</t>
+          <t>Referee Title</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>referee_department</t>
+          <t>referee_institution</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>referee_department</t>
+          <t>Referee Institution</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>referee_department</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>Referee Department</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>reference_type</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>reference_type</t>
+          <t>Rating</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>reference_length</t>
+          <t>is_reference</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>reference_length</t>
+          <t>Is the referee a reference for the submitter?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>referee_comment</t>
+          <t>reference_type</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>referee_comment</t>
+          <t>Reference Type</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>referee_letter</t>
+          <t>reference_length</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>referee_letter</t>
+          <t>Reference Length</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>referee_signature</t>
+          <t>referee_comment</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>referee_signature</t>
+          <t>Referee Comment</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>referee_letter_attachment</t>
+          <t>referee_letter</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>referee_letter_attachment</t>
+          <t>Referee Letter</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>referee_letter_other_attachment</t>
+          <t>referee_signature</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>referee_letter_other_attachment</t>
+          <t>Referee Signature</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>date_submitted</t>
+          <t>referee_letter_attachment</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>date_submitted</t>
+          <t>Referee Letter Attachment</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>time_submitted</t>
+          <t>referee_other_attachment</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>time_submitted</t>
+          <t>Other Referee Letter Attachment</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>time_submitted</t>
+          <t>date_submitted</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Time Submitted</t>
+          <t>Date Submitted</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>date_submitted</t>
+          <t>time_submitted</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Date Submitted</t>
+          <t>Time Submitted</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>referee_phone</t>
+          <t>Referee Phone</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>referee_email</t>
+          <t>Referee Email</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>referee_institution</t>
+          <t>referee_institution_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>referee_institution</t>
+          <t>Referee Institution 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>submitter_institution</t>
+          <t>Submitter Institution</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>referee_address</t>
+          <t>Referee Address</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>referee_zip</t>
+          <t>Referee Zip</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>referee_city</t>
+          <t>Referee City</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>referee_state</t>
+          <t>Referee State</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,11 +1098,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -1126,34 +1126,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>submitter_choices</t>
+          <t>is_submitter_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>submitter_choices</t>
+          <t>is_submitter_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1182,182 +1182,216 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>reference_type_choices</t>
+          <t>is_reference_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>reference_type_choices</t>
+          <t>is_reference_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>reference_length_choices</t>
+          <t>reference_type_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>reference_length_choices</t>
+          <t>reference_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>referee_institution_choices</t>
+          <t>reference_length_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>referee_institution_choices</t>
+          <t>reference_length_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>submitter_institution_choices</t>
+          <t>referee_institution_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>submitter_institution_choices</t>
+          <t>referee_institution_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>referee_state_choices</t>
+          <t>submitter_institution_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>submitter_institution_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>referee_state_choices</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>referee_state_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
